--- a/tasks/finalpool/wc-sf-support-quality-review/groundtruth_workspace/CX_Quality_Review.xlsx
+++ b/tasks/finalpool/wc-sf-support-quality-review/groundtruth_workspace/CX_Quality_Review.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,48 +492,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Home Appliances</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TV &amp; Home Theater</t>
+          <t>Home Appliances</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Watches</t>
+          <t>Speakers</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TV &amp; Home Theater</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Watches</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>15.8</v>
       </c>
     </row>
@@ -715,7 +747,7 @@
         <v>6804</v>
       </c>
       <c r="C2" t="n">
-        <v>14.65</v>
+        <v>15.96</v>
       </c>
       <c r="D2" t="n">
         <v>2.96</v>
@@ -731,7 +763,7 @@
         <v>6118</v>
       </c>
       <c r="C3" t="n">
-        <v>13.4</v>
+        <v>14.63</v>
       </c>
       <c r="D3" t="n">
         <v>3.31</v>
@@ -747,7 +779,7 @@
         <v>4463</v>
       </c>
       <c r="C4" t="n">
-        <v>13.39</v>
+        <v>14.61</v>
       </c>
       <c r="D4" t="n">
         <v>3.31</v>
@@ -763,10 +795,10 @@
         <v>1558</v>
       </c>
       <c r="C5" t="n">
-        <v>13.37</v>
+        <v>14.67</v>
       </c>
       <c r="D5" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6">
@@ -779,7 +811,7 @@
         <v>8128</v>
       </c>
       <c r="C6" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="D6" t="n">
         <v>3.38</v>
@@ -795,7 +827,7 @@
         <v>3002</v>
       </c>
       <c r="C7" t="n">
-        <v>13.26</v>
+        <v>14.27</v>
       </c>
       <c r="D7" t="n">
         <v>3.31</v>
@@ -811,7 +843,7 @@
         <v>1515</v>
       </c>
       <c r="C8" t="n">
-        <v>13.56</v>
+        <v>14.7</v>
       </c>
       <c r="D8" t="n">
         <v>3.35</v>
@@ -850,7 +882,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3">
@@ -860,7 +892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="4">
